--- a/ig/DM-AOUT-2026/ValueSet-JDV-J133-ActiviteSanitaireRegulee-RASS.xlsx
+++ b/ig/DM-AOUT-2026/ValueSet-JDV-J133-ActiviteSanitaireRegulee-RASS.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="163">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="187">
   <si>
     <t>Property</t>
   </si>
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20201127120000</t>
+    <t>20260827120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2020-11-27T12:00:00+01:00</t>
+    <t>2026-08-27T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -493,6 +493,78 @@
   </si>
   <si>
     <t>SSRS - Viroses chroniques</t>
+  </si>
+  <si>
+    <t>A8</t>
+  </si>
+  <si>
+    <t>Greffe de face ou de face inférieure</t>
+  </si>
+  <si>
+    <t>A9</t>
+  </si>
+  <si>
+    <t>Greffe unilatérale ou bilatérale de main</t>
+  </si>
+  <si>
+    <t>B0</t>
+  </si>
+  <si>
+    <t>Prélèvement de cellules mononuclées autologues</t>
+  </si>
+  <si>
+    <t>B1</t>
+  </si>
+  <si>
+    <t>Prélèvement de cellules mononuclées allogéniques</t>
+  </si>
+  <si>
+    <t>C1</t>
+  </si>
+  <si>
+    <t>Greffe unilatérale ou bilatérale d'avant-bras</t>
+  </si>
+  <si>
+    <t>C3</t>
+  </si>
+  <si>
+    <t>Greffe unilatérale ou bilatérale de bras</t>
+  </si>
+  <si>
+    <t>D1</t>
+  </si>
+  <si>
+    <t>Greffe de membre inférieur</t>
+  </si>
+  <si>
+    <t>F4</t>
+  </si>
+  <si>
+    <t>Greffe de langue</t>
+  </si>
+  <si>
+    <t>F9</t>
+  </si>
+  <si>
+    <t>Greffe de pénis</t>
+  </si>
+  <si>
+    <t>H2</t>
+  </si>
+  <si>
+    <t>Greffe de paroi abdominale</t>
+  </si>
+  <si>
+    <t>H3</t>
+  </si>
+  <si>
+    <t>Greffe de tissus cutanés conjonctifs et vasculo- nerveux</t>
+  </si>
+  <si>
+    <t>S8</t>
+  </si>
+  <si>
+    <t>Maison de naissance</t>
   </si>
   <si>
     <t/>
@@ -763,7 +835,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B69"/>
+  <dimension ref="A1:B81"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -1311,15 +1383,111 @@
         <v>160</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="B70" t="s" s="2">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="B71" t="s" s="2">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="B72" t="s" s="2">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="B73" t="s" s="2">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="s" s="2">
+        <v>172</v>
+      </c>
+      <c r="B74" t="s" s="2">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="B75" t="s" s="2">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="B76" t="s" s="2">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="B77" t="s" s="2">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="B78" t="s" s="2">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="B79" t="s" s="2">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="B80" t="s" s="2">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="B81" t="s" s="2">
+        <v>186</v>
       </c>
     </row>
   </sheetData>
